--- a/Tools/Config/Datas/__tables__.xlsx
+++ b/Tools/Config/Datas/__tables__.xlsx
@@ -1032,7 +1032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="28.5833333333333" customWidth="1" style="4" min="2" max="2"/>
@@ -1334,22 +1334,117 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>DazeSettingReader</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>DazeSetting</t>
         </is>
       </c>
-      <c r="D10" t="b">
+      <c r="D10" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>Daze@DazeSetting.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>CharacterKitReader</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>CharacterKitSetting</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>CharacterKit@CharacterSetting.xlsx</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>CharacterId</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>角色招式包：被动 + Z 响应技</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>CharacterSlotReader</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>CharacterSlotSetting</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>CharacterSlot@CharacterSetting.xlsx</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>CharacterId+Button+Press+FormId+Priority</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>角色 4 战斗键 Idle 入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SquadSettingReader</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SquadSetting</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Squad@SquadSetting.xlsx</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>小队换人：支援窗 / 支援点 / i-frame</t>
         </is>
       </c>
     </row>

--- a/Tools/Config/Datas/__tables__.xlsx
+++ b/Tools/Config/Datas/__tables__.xlsx
@@ -1032,7 +1032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="28.5833333333333" customWidth="1" style="4" min="2" max="2"/>
@@ -1419,32 +1419,131 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>SquadSettingReader</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>SquadSetting</t>
         </is>
       </c>
-      <c r="D13" t="b">
+      <c r="D13" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>Squad@SquadSetting.xlsx</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t>小队换人：支援窗 / 支援点 / i-frame</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="n"/>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>MonsterReader</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>MonsterSetting</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Monster@MonsterSetting.xlsx</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>MonsterId</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="n"/>
+      <c r="H14" s="0" t="n"/>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>怪物身份列表，主键 MonsterId</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="n"/>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>VibrationSettingReader</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>VibrationSetting</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>VibrationSetting@MonsterSetting.xlsx</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>MonsterId</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="n"/>
+      <c r="H15" s="0" t="n"/>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>共振度按怪物；缺行=无条，不回退</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="n"/>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>VibrationRuleReader</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>VibrationRule</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>VibrationRule@MonsterSetting.xlsx</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="n"/>
+      <c r="H16" s="0" t="n"/>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>招架/谐度破坏削韧全局一行 Id=1</t>
         </is>
       </c>
     </row>
